--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_DRIPOW-CSTD-1-00-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_H_DRIPOW-CSTD-1-00-B-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\ソフトチーム\20260106_REMWAR_RW\045\IpcApplication\Vom\Alert\matrix\scc\ref更新\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B893F392-5DA3-4C35-8193-0C884E2CEA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43299662-B2A5-4750-B58A-60E269F097E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="696" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="2130" windowWidth="22740" windowHeight="14070" tabRatio="696" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -29,22 +29,21 @@
     <externalReference r:id="rId12"/>
     <externalReference r:id="rId13"/>
     <externalReference r:id="rId14"/>
-    <externalReference r:id="rId15"/>
   </externalReferences>
   <definedNames>
     <definedName name="_1AB030_" localSheetId="0" hidden="1">{"A",#N/A,FALSE,"(部)工程別 ";"B",#N/A,FALSE,"(部)工程別 ";"D",#N/A,FALSE,"(部)工程別 "}</definedName>
     <definedName name="_1AB030_" hidden="1">{"A",#N/A,FALSE,"(部)工程別 ";"B",#N/A,FALSE,"(部)工程別 ";"D",#N/A,FALSE,"(部)工程別 "}</definedName>
     <definedName name="_2AB926_" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="_2AB926_" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
-    <definedName name="_Fill" hidden="1">'[2]#REF'!$C$3:$C$1000</definedName>
-    <definedName name="_Key1" hidden="1">'[2]#REF'!$A$3</definedName>
+    <definedName name="_Fill" hidden="1">'[1]#REF'!$C$3:$C$1000</definedName>
+    <definedName name="_Key1" hidden="1">'[1]#REF'!$A$3</definedName>
     <definedName name="_MatInverse_In" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="_MatInverse_In" hidden="1">#REF!</definedName>
     <definedName name="_MatInverse_Out" localSheetId="0" hidden="1">#REF!</definedName>
     <definedName name="_MatInverse_Out" hidden="1">#REF!</definedName>
     <definedName name="_Order1" hidden="1">255</definedName>
     <definedName name="_Order2" hidden="1">1</definedName>
-    <definedName name="_Sort" hidden="1">'[2]#REF'!$A$3:$AE$787</definedName>
+    <definedName name="_Sort" hidden="1">'[1]#REF'!$A$3:$AE$787</definedName>
     <definedName name="A">#REF!</definedName>
     <definedName name="ADLSB">#REF!</definedName>
     <definedName name="B">#REF!</definedName>
@@ -76,8 +75,8 @@
     <definedName name="IG">#REF!</definedName>
     <definedName name="K">#REF!</definedName>
     <definedName name="LED">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area">[4]Sheet1!$A$1:$I$233</definedName>
-    <definedName name="_xlnm.Print_Titles">[5]車両仕様!$A$1:$C$65536,[5]車両仕様!$A$3:$IV$4</definedName>
+    <definedName name="_xlnm.Print_Area">[2]Sheet1!$A$1:$I$233</definedName>
+    <definedName name="_xlnm.Print_Titles">[3]車両仕様!$A$1:$C$65536,[3]車両仕様!$A$3:$IV$4</definedName>
     <definedName name="ｓ">#REF!</definedName>
     <definedName name="Sheet_dspmaincfg_Top">#REF!</definedName>
     <definedName name="Sheet_ユーザーカスタマイズ手順_Top">#REF!</definedName>
@@ -193,16 +192,16 @@
     <definedName name="愛" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="開発費" localSheetId="0" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
     <definedName name="開発費" hidden="1">{#N/A,#N/A,FALSE,"96下820";#N/A,#N/A,FALSE,"96下826";#N/A,#N/A,FALSE,"96下827";#N/A,#N/A,FALSE,"96下828";#N/A,#N/A,FALSE,"96下861";#N/A,#N/A,FALSE,"96下862"}</definedName>
-    <definedName name="関数名_確定_BON">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGOFF">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_IGON">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_WKUP">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_0">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_1">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_2">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_3">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_状態遷移_4">'[6]Config - dspmgr'!#REF!</definedName>
-    <definedName name="関数名_確定_定期">'[6]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_BON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGOFF">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_IGON">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_WKUP">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_0">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_1">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_2">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_3">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_状態遷移_4">'[4]Config - dspmgr'!#REF!</definedName>
+    <definedName name="関数名_確定_定期">'[4]Config - dspmgr'!#REF!</definedName>
     <definedName name="金型共通化" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
     <definedName name="金型共通化２" localSheetId="0" hidden="1">{"A",#N/A,TRUE,"(原)提出";"B",#N/A,TRUE,"(原)提出";"D",#N/A,TRUE,"(原)提出";"E",#N/A,TRUE,"(原)提出"}</definedName>
@@ -723,7 +722,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2727" uniqueCount="354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2729" uniqueCount="356">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -3584,6 +3583,25 @@
     <t xml:space="preserve"> </t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>RWの削除
+[Reference]シート
+RW記載を対象外に変更</t>
+    <rPh sb="23" eb="25">
+      <t>キサイ</t>
+    </rPh>
+    <rPh sb="26" eb="29">
+      <t>タイショウガイ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2.2.0</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
@@ -3942,7 +3960,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="86">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -5045,6 +5063,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -5057,7 +5088,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="322">
+  <cellXfs count="336">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5778,17 +5809,110 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="32" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="17" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5800,6 +5924,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="86" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5823,37 +5953,16 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5898,10 +6007,31 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5954,63 +6084,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="64" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="66" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="65" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="85" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="84" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="29" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="2" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -7140,7 +7213,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="[1]MID!$D$2:$AD$27" spid="_x0000_s1544"/>
+                  <a14:cameraTool cellRange="[5]MID!$D$2:$AD$27" spid="_x0000_s1560"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7205,7 +7278,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="[1]TT!$D$2:$O$25" spid="_x0000_s1545"/>
+                  <a14:cameraTool cellRange="[5]TT!$D$2:$O$25" spid="_x0000_s1561"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -7270,7 +7343,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="[1]TT!$D$26:$U$49" spid="_x0000_s1546"/>
+                  <a14:cameraTool cellRange="[5]TT!$D$26:$U$49" spid="_x0000_s1562"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -11525,7 +11598,7 @@
               <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
               <a:extLst>
                 <a:ext uri="{84589F7E-364E-4C9E-8A38-B11213B215E9}">
-                  <a14:cameraTool cellRange="'[1]Detailed Spec'!$D$57:$H$67" spid="_x0000_s1547"/>
+                  <a14:cameraTool cellRange="'[5]Detailed Spec'!$D$57:$H$67" spid="_x0000_s1563"/>
                 </a:ext>
               </a:extLst>
             </xdr:cNvPicPr>
@@ -12167,108 +12240,374 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>557894</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E04E294-E3CA-4439-8A96-F9FBA1993CFA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15933965" y="911679"/>
+          <a:ext cx="3429000" cy="7456714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="正方形/長方形 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CED7695F-DDA0-4CE5-851D-021F14ABC3A3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="33092571" y="3320143"/>
+          <a:ext cx="5442858" cy="1741714"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>264</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>51</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>285</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="正方形/長方形 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AC105DFD-E076-454D-9A98-636E01366151}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14733494" y="47770676"/>
+          <a:ext cx="24587947" cy="3529853"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>150</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="正方形/長方形 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14E43086-6815-4369-9353-E4C40D6F0EDF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14273894" y="29772429"/>
+          <a:ext cx="4531178" cy="4953000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent3">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>RW</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1400" b="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>削除対応</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="TT"/>
-      <sheetName val="BZR"/>
-      <sheetName val="MID"/>
-      <sheetName val="MSG"/>
-      <sheetName val="Variable_MID"/>
-      <sheetName val="Variable_MSG"/>
-      <sheetName val="SW"/>
-      <sheetName val="SW_MSG"/>
-      <sheetName val="Revision history"/>
-      <sheetName val="Detailed Spec"/>
-      <sheetName val="Detailed Spec2"/>
-      <sheetName val="Detailed Spec3"/>
-      <sheetName val="Item_Property_List"/>
-      <sheetName val="Message"/>
-      <sheetName val="DataInputRule"/>
-      <sheetName val="DataInputRule_ja"/>
-      <sheetName val="DataInputRule_en"/>
-      <sheetName val="TT_ja"/>
-      <sheetName val="TT_en"/>
-      <sheetName val="BZR_ja"/>
-      <sheetName val="BZR_en"/>
-      <sheetName val="MID_ja"/>
-      <sheetName val="MID_en"/>
-      <sheetName val="MSG_ja"/>
-      <sheetName val="MSG_en"/>
-      <sheetName val="Detailed Spec_ja"/>
-      <sheetName val="Detailed Spec_en"/>
-      <sheetName val="Variable_MID_ja"/>
-      <sheetName val="Variable_MID_en"/>
-      <sheetName val="Variable_MSG_ja"/>
-      <sheetName val="Variable_MSG_en"/>
-      <sheetName val="SW_ja"/>
-      <sheetName val="SW_en"/>
-      <sheetName val="SW_MSG_ja"/>
-      <sheetName val="SW_MSG_en"/>
-      <sheetName val="Detailed Spec2_ja"/>
-      <sheetName val="Detailed Spec2_en"/>
-      <sheetName val="Detailed Spec3_ja"/>
-      <sheetName val="Detailed Spec3_en"/>
-      <sheetName val="Revision history_ja"/>
-      <sheetName val="Revision history_en"/>
-      <sheetName val="Restore_Macro"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -12573,57 +12912,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="表紙（承認欄）"/>
-      <sheetName val="変更履歴"/>
-      <sheetName val="要件分析, ソフト分析"/>
-      <sheetName val="課題リスト"/>
-      <sheetName val="MAPPING(Featureのみ)"/>
-      <sheetName val="Evidence(Featureのみ)"/>
-      <sheetName val="MAPPING"/>
-      <sheetName val="param"/>
-      <sheetName val="Evidence"/>
-      <sheetName val="2. 仕様差分の確認結果(for traceability)"/>
-      <sheetName val="2. 仕様差分の確認結果(for visibility)"/>
-      <sheetName val="2-1.要件分析_ストラテジ"/>
-      <sheetName val="3. 関連仕様の確認結果_詳細"/>
-      <sheetName val="設計・評価方針(仕様変化点_設計方針から抽出)"/>
-      <sheetName val="4. ソフト変更方法の詳細"/>
-      <sheetName val="ブロック図(概要)"/>
-      <sheetName val="留意点に対する設計結果_詳細"/>
-      <sheetName val="5.ソフト影響箇所の確認_詳細"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -12998,7 +13287,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -28211,7 +28500,7 @@
 </externalLink>
 </file>
 
-<file path=xl/externalLinks/externalLink6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
@@ -28512,6 +28801,104 @@
 </externalLink>
 </file>
 
+<file path=xl/externalLinks/externalLink5.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="TT"/>
+      <sheetName val="BZR"/>
+      <sheetName val="MID"/>
+      <sheetName val="MSG"/>
+      <sheetName val="Variable_MID"/>
+      <sheetName val="Variable_MSG"/>
+      <sheetName val="SW"/>
+      <sheetName val="SW_MSG"/>
+      <sheetName val="Revision history"/>
+      <sheetName val="Detailed Spec"/>
+      <sheetName val="Detailed Spec2"/>
+      <sheetName val="Detailed Spec3"/>
+      <sheetName val="Item_Property_List"/>
+      <sheetName val="Message"/>
+      <sheetName val="DataInputRule"/>
+      <sheetName val="DataInputRule_ja"/>
+      <sheetName val="DataInputRule_en"/>
+      <sheetName val="TT_ja"/>
+      <sheetName val="TT_en"/>
+      <sheetName val="BZR_ja"/>
+      <sheetName val="BZR_en"/>
+      <sheetName val="MID_ja"/>
+      <sheetName val="MID_en"/>
+      <sheetName val="MSG_ja"/>
+      <sheetName val="MSG_en"/>
+      <sheetName val="Detailed Spec_ja"/>
+      <sheetName val="Detailed Spec_en"/>
+      <sheetName val="Variable_MID_ja"/>
+      <sheetName val="Variable_MID_en"/>
+      <sheetName val="Variable_MSG_ja"/>
+      <sheetName val="Variable_MSG_en"/>
+      <sheetName val="SW_ja"/>
+      <sheetName val="SW_en"/>
+      <sheetName val="SW_MSG_ja"/>
+      <sheetName val="SW_MSG_en"/>
+      <sheetName val="Detailed Spec2_ja"/>
+      <sheetName val="Detailed Spec2_en"/>
+      <sheetName val="Detailed Spec3_ja"/>
+      <sheetName val="Detailed Spec3_en"/>
+      <sheetName val="Revision history_ja"/>
+      <sheetName val="Revision history_en"/>
+      <sheetName val="Restore_Macro"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+      <sheetData sheetId="6" refreshError="1"/>
+      <sheetData sheetId="7" refreshError="1"/>
+      <sheetData sheetId="8" refreshError="1"/>
+      <sheetData sheetId="9"/>
+      <sheetData sheetId="10" refreshError="1"/>
+      <sheetData sheetId="11" refreshError="1"/>
+      <sheetData sheetId="12" refreshError="1"/>
+      <sheetData sheetId="13" refreshError="1"/>
+      <sheetData sheetId="14" refreshError="1"/>
+      <sheetData sheetId="15" refreshError="1"/>
+      <sheetData sheetId="16" refreshError="1"/>
+      <sheetData sheetId="17" refreshError="1"/>
+      <sheetData sheetId="18" refreshError="1"/>
+      <sheetData sheetId="19" refreshError="1"/>
+      <sheetData sheetId="20" refreshError="1"/>
+      <sheetData sheetId="21" refreshError="1"/>
+      <sheetData sheetId="22" refreshError="1"/>
+      <sheetData sheetId="23" refreshError="1"/>
+      <sheetData sheetId="24" refreshError="1"/>
+      <sheetData sheetId="25" refreshError="1"/>
+      <sheetData sheetId="26" refreshError="1"/>
+      <sheetData sheetId="27" refreshError="1"/>
+      <sheetData sheetId="28" refreshError="1"/>
+      <sheetData sheetId="29" refreshError="1"/>
+      <sheetData sheetId="30" refreshError="1"/>
+      <sheetData sheetId="31" refreshError="1"/>
+      <sheetData sheetId="32" refreshError="1"/>
+      <sheetData sheetId="33" refreshError="1"/>
+      <sheetData sheetId="34" refreshError="1"/>
+      <sheetData sheetId="35" refreshError="1"/>
+      <sheetData sheetId="36" refreshError="1"/>
+      <sheetData sheetId="37" refreshError="1"/>
+      <sheetData sheetId="38" refreshError="1"/>
+      <sheetData sheetId="39" refreshError="1"/>
+      <sheetData sheetId="40" refreshError="1"/>
+      <sheetData sheetId="41" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -28803,10 +29190,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="52" width="2.26953125" style="303" customWidth="1"/>
-    <col min="53" max="16384" width="8.81640625" style="303"/>
+    <col min="1" max="52" width="2.25" style="244" customWidth="1"/>
+    <col min="53" max="16384" width="8.875" style="244"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -28819,12 +29206,12 @@
     <row r="8" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="9" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="10" spans="6:20" ht="13.15" customHeight="1">
-      <c r="F10" s="304"/>
+      <c r="F10" s="245"/>
     </row>
     <row r="11" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="12" spans="6:20" ht="13.15" customHeight="1"/>
     <row r="13" spans="6:20" ht="13.15" customHeight="1">
-      <c r="T13" s="305" t="str">
+      <c r="T13" s="246" t="str">
         <f ca="1">MID(CELL("filename",A1),FIND("[",CELL("filename",A1))+1,FIND("]",CELL("filename",A1))-FIND("[",CELL("filename",A1))-1)</f>
         <v>alert_H_DRIPOW-CSTD-1-00-B-C0.xlsx</v>
       </c>
@@ -28848,20 +29235,20 @@
     <row r="30" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="31" spans="3:22" ht="13.15" customHeight="1"/>
     <row r="32" spans="3:22" ht="13.15" customHeight="1">
-      <c r="C32" s="306"/>
-      <c r="V32" s="306"/>
+      <c r="C32" s="247"/>
+      <c r="V32" s="247"/>
     </row>
     <row r="33" spans="3:39" ht="13.15" customHeight="1">
-      <c r="M33" s="307"/>
-      <c r="N33" s="307"/>
-      <c r="O33" s="307"/>
-      <c r="P33" s="307"/>
-      <c r="Q33" s="307"/>
-      <c r="AF33" s="307"/>
-      <c r="AG33" s="307"/>
-      <c r="AH33" s="307"/>
-      <c r="AI33" s="307"/>
-      <c r="AJ33" s="307"/>
+      <c r="M33" s="248"/>
+      <c r="N33" s="248"/>
+      <c r="O33" s="248"/>
+      <c r="P33" s="248"/>
+      <c r="Q33" s="248"/>
+      <c r="AF33" s="248"/>
+      <c r="AG33" s="248"/>
+      <c r="AH33" s="248"/>
+      <c r="AI33" s="248"/>
+      <c r="AJ33" s="248"/>
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="150" t="s">
@@ -28869,354 +29256,354 @@
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="308" t="s">
+      <c r="Y35" s="274" t="s">
         <v>340</v>
       </c>
-      <c r="Z35" s="309"/>
-      <c r="AA35" s="309"/>
-      <c r="AB35" s="309"/>
-      <c r="AC35" s="310"/>
-      <c r="AD35" s="308" t="s">
+      <c r="Z35" s="275"/>
+      <c r="AA35" s="275"/>
+      <c r="AB35" s="275"/>
+      <c r="AC35" s="276"/>
+      <c r="AD35" s="274" t="s">
         <v>341</v>
       </c>
-      <c r="AE35" s="309"/>
-      <c r="AF35" s="309"/>
-      <c r="AG35" s="309"/>
-      <c r="AH35" s="310"/>
-      <c r="AI35" s="308" t="s">
+      <c r="AE35" s="275"/>
+      <c r="AF35" s="275"/>
+      <c r="AG35" s="275"/>
+      <c r="AH35" s="276"/>
+      <c r="AI35" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="AJ35" s="309"/>
-      <c r="AK35" s="309"/>
-      <c r="AL35" s="309"/>
-      <c r="AM35" s="310"/>
+      <c r="AJ35" s="275"/>
+      <c r="AK35" s="275"/>
+      <c r="AL35" s="275"/>
+      <c r="AM35" s="276"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D36" s="307"/>
-      <c r="E36" s="311"/>
-      <c r="F36" s="307"/>
-      <c r="G36" s="307"/>
-      <c r="I36" s="307"/>
-      <c r="J36" s="311"/>
-      <c r="K36" s="307"/>
-      <c r="L36" s="307"/>
-      <c r="M36" s="307"/>
-      <c r="N36" s="307"/>
-      <c r="O36" s="311"/>
-      <c r="P36" s="307"/>
-      <c r="Q36" s="307"/>
-      <c r="W36" s="307"/>
-      <c r="X36" s="311"/>
-      <c r="Y36" s="312"/>
-      <c r="Z36" s="313"/>
-      <c r="AA36" s="313"/>
-      <c r="AB36" s="313"/>
-      <c r="AC36" s="314"/>
-      <c r="AD36" s="312"/>
-      <c r="AE36" s="313"/>
-      <c r="AF36" s="313"/>
-      <c r="AG36" s="313"/>
-      <c r="AH36" s="314"/>
-      <c r="AI36" s="312"/>
-      <c r="AJ36" s="313"/>
-      <c r="AK36" s="313"/>
-      <c r="AL36" s="313"/>
-      <c r="AM36" s="314"/>
+      <c r="D36" s="248"/>
+      <c r="E36" s="249"/>
+      <c r="F36" s="248"/>
+      <c r="G36" s="248"/>
+      <c r="I36" s="248"/>
+      <c r="J36" s="249"/>
+      <c r="K36" s="248"/>
+      <c r="L36" s="248"/>
+      <c r="M36" s="248"/>
+      <c r="N36" s="248"/>
+      <c r="O36" s="249"/>
+      <c r="P36" s="248"/>
+      <c r="Q36" s="248"/>
+      <c r="W36" s="248"/>
+      <c r="X36" s="249"/>
+      <c r="Y36" s="250"/>
+      <c r="Z36" s="251"/>
+      <c r="AA36" s="251"/>
+      <c r="AB36" s="251"/>
+      <c r="AC36" s="252"/>
+      <c r="AD36" s="250"/>
+      <c r="AE36" s="251"/>
+      <c r="AF36" s="251"/>
+      <c r="AG36" s="251"/>
+      <c r="AH36" s="252"/>
+      <c r="AI36" s="250"/>
+      <c r="AJ36" s="251"/>
+      <c r="AK36" s="251"/>
+      <c r="AL36" s="251"/>
+      <c r="AM36" s="252"/>
     </row>
     <row r="37" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y37" s="315"/>
-      <c r="AC37" s="316"/>
-      <c r="AD37" s="315"/>
-      <c r="AH37" s="316"/>
-      <c r="AI37" s="315"/>
-      <c r="AM37" s="316"/>
+      <c r="Y37" s="253"/>
+      <c r="AC37" s="254"/>
+      <c r="AD37" s="253"/>
+      <c r="AH37" s="254"/>
+      <c r="AI37" s="253"/>
+      <c r="AM37" s="254"/>
     </row>
     <row r="38" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y38" s="315"/>
-      <c r="Z38" s="307"/>
-      <c r="AA38" s="311" t="s">
+      <c r="Y38" s="253"/>
+      <c r="Z38" s="248"/>
+      <c r="AA38" s="249" t="s">
         <v>343</v>
       </c>
-      <c r="AB38" s="307"/>
-      <c r="AC38" s="317"/>
-      <c r="AD38" s="315"/>
-      <c r="AE38" s="307"/>
-      <c r="AF38" s="311" t="s">
+      <c r="AB38" s="248"/>
+      <c r="AC38" s="255"/>
+      <c r="AD38" s="253"/>
+      <c r="AE38" s="248"/>
+      <c r="AF38" s="249" t="s">
         <v>344</v>
       </c>
-      <c r="AG38" s="307"/>
-      <c r="AH38" s="317"/>
-      <c r="AI38" s="318"/>
-      <c r="AJ38" s="307"/>
-      <c r="AK38" s="311" t="s">
+      <c r="AG38" s="248"/>
+      <c r="AH38" s="255"/>
+      <c r="AI38" s="256"/>
+      <c r="AJ38" s="248"/>
+      <c r="AK38" s="249" t="s">
         <v>345</v>
       </c>
-      <c r="AL38" s="307"/>
-      <c r="AM38" s="317"/>
+      <c r="AL38" s="248"/>
+      <c r="AM38" s="255"/>
     </row>
     <row r="39" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y39" s="315"/>
-      <c r="AC39" s="316"/>
-      <c r="AD39" s="315"/>
-      <c r="AH39" s="316"/>
-      <c r="AI39" s="315"/>
-      <c r="AM39" s="316"/>
+      <c r="Y39" s="253"/>
+      <c r="AC39" s="254"/>
+      <c r="AD39" s="253"/>
+      <c r="AH39" s="254"/>
+      <c r="AI39" s="253"/>
+      <c r="AM39" s="254"/>
     </row>
     <row r="40" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C40" s="306"/>
-      <c r="V40" s="306"/>
-      <c r="Y40" s="319"/>
-      <c r="Z40" s="320"/>
-      <c r="AA40" s="320"/>
-      <c r="AB40" s="320"/>
-      <c r="AC40" s="321"/>
-      <c r="AD40" s="319"/>
-      <c r="AE40" s="320"/>
-      <c r="AF40" s="320"/>
-      <c r="AG40" s="320"/>
-      <c r="AH40" s="321"/>
-      <c r="AI40" s="319"/>
-      <c r="AJ40" s="320"/>
-      <c r="AK40" s="320"/>
-      <c r="AL40" s="320"/>
-      <c r="AM40" s="321"/>
+      <c r="C40" s="247"/>
+      <c r="V40" s="247"/>
+      <c r="Y40" s="257"/>
+      <c r="Z40" s="258"/>
+      <c r="AA40" s="258"/>
+      <c r="AB40" s="258"/>
+      <c r="AC40" s="259"/>
+      <c r="AD40" s="257"/>
+      <c r="AE40" s="258"/>
+      <c r="AF40" s="258"/>
+      <c r="AG40" s="258"/>
+      <c r="AH40" s="259"/>
+      <c r="AI40" s="257"/>
+      <c r="AJ40" s="258"/>
+      <c r="AK40" s="258"/>
+      <c r="AL40" s="258"/>
+      <c r="AM40" s="259"/>
     </row>
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y42" s="306" t="s">
+      <c r="Y42" s="247" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="308" t="s">
+      <c r="Y43" s="274" t="s">
         <v>340</v>
       </c>
-      <c r="Z43" s="309"/>
-      <c r="AA43" s="309"/>
-      <c r="AB43" s="309"/>
-      <c r="AC43" s="310"/>
-      <c r="AD43" s="308" t="s">
+      <c r="Z43" s="275"/>
+      <c r="AA43" s="275"/>
+      <c r="AB43" s="275"/>
+      <c r="AC43" s="276"/>
+      <c r="AD43" s="274" t="s">
         <v>341</v>
       </c>
-      <c r="AE43" s="309"/>
-      <c r="AF43" s="309"/>
-      <c r="AG43" s="309"/>
-      <c r="AH43" s="310"/>
-      <c r="AI43" s="308" t="s">
+      <c r="AE43" s="275"/>
+      <c r="AF43" s="275"/>
+      <c r="AG43" s="275"/>
+      <c r="AH43" s="276"/>
+      <c r="AI43" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="AJ43" s="309"/>
-      <c r="AK43" s="309"/>
-      <c r="AL43" s="309"/>
-      <c r="AM43" s="310"/>
+      <c r="AJ43" s="275"/>
+      <c r="AK43" s="275"/>
+      <c r="AL43" s="275"/>
+      <c r="AM43" s="276"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
-      <c r="D44" s="307"/>
-      <c r="E44" s="311"/>
-      <c r="F44" s="307"/>
-      <c r="G44" s="307"/>
-      <c r="H44" s="307"/>
-      <c r="I44" s="307"/>
-      <c r="J44" s="311"/>
-      <c r="K44" s="307"/>
-      <c r="L44" s="307"/>
-      <c r="M44" s="307"/>
-      <c r="N44" s="307"/>
-      <c r="O44" s="311"/>
-      <c r="P44" s="307"/>
-      <c r="Q44" s="307"/>
-      <c r="W44" s="307"/>
-      <c r="X44" s="311"/>
-      <c r="Y44" s="312"/>
-      <c r="Z44" s="313"/>
-      <c r="AA44" s="313"/>
-      <c r="AB44" s="313"/>
-      <c r="AC44" s="314"/>
-      <c r="AD44" s="313"/>
-      <c r="AE44" s="313"/>
-      <c r="AF44" s="313"/>
-      <c r="AG44" s="313"/>
-      <c r="AH44" s="314"/>
-      <c r="AI44" s="312"/>
-      <c r="AJ44" s="313"/>
-      <c r="AK44" s="313"/>
-      <c r="AL44" s="313"/>
-      <c r="AM44" s="314"/>
+      <c r="D44" s="248"/>
+      <c r="E44" s="249"/>
+      <c r="F44" s="248"/>
+      <c r="G44" s="248"/>
+      <c r="H44" s="248"/>
+      <c r="I44" s="248"/>
+      <c r="J44" s="249"/>
+      <c r="K44" s="248"/>
+      <c r="L44" s="248"/>
+      <c r="M44" s="248"/>
+      <c r="N44" s="248"/>
+      <c r="O44" s="249"/>
+      <c r="P44" s="248"/>
+      <c r="Q44" s="248"/>
+      <c r="W44" s="248"/>
+      <c r="X44" s="249"/>
+      <c r="Y44" s="250"/>
+      <c r="Z44" s="251"/>
+      <c r="AA44" s="251"/>
+      <c r="AB44" s="251"/>
+      <c r="AC44" s="252"/>
+      <c r="AD44" s="251"/>
+      <c r="AE44" s="251"/>
+      <c r="AF44" s="251"/>
+      <c r="AG44" s="251"/>
+      <c r="AH44" s="252"/>
+      <c r="AI44" s="250"/>
+      <c r="AJ44" s="251"/>
+      <c r="AK44" s="251"/>
+      <c r="AL44" s="251"/>
+      <c r="AM44" s="252"/>
     </row>
     <row r="45" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y45" s="315"/>
-      <c r="AC45" s="316"/>
-      <c r="AH45" s="316"/>
-      <c r="AI45" s="315"/>
-      <c r="AM45" s="316"/>
+      <c r="Y45" s="253"/>
+      <c r="AC45" s="254"/>
+      <c r="AH45" s="254"/>
+      <c r="AI45" s="253"/>
+      <c r="AM45" s="254"/>
     </row>
     <row r="46" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y46" s="315"/>
-      <c r="Z46" s="307"/>
-      <c r="AA46" s="311" t="s">
+      <c r="Y46" s="253"/>
+      <c r="Z46" s="248"/>
+      <c r="AA46" s="249" t="s">
         <v>347</v>
       </c>
-      <c r="AB46" s="307"/>
-      <c r="AC46" s="317"/>
-      <c r="AD46" s="307"/>
-      <c r="AE46" s="307"/>
-      <c r="AF46" s="311" t="s">
+      <c r="AB46" s="248"/>
+      <c r="AC46" s="255"/>
+      <c r="AD46" s="248"/>
+      <c r="AE46" s="248"/>
+      <c r="AF46" s="249" t="s">
         <v>348</v>
       </c>
-      <c r="AG46" s="307"/>
-      <c r="AH46" s="317"/>
-      <c r="AI46" s="318"/>
-      <c r="AJ46" s="307"/>
-      <c r="AK46" s="311" t="s">
+      <c r="AG46" s="248"/>
+      <c r="AH46" s="255"/>
+      <c r="AI46" s="256"/>
+      <c r="AJ46" s="248"/>
+      <c r="AK46" s="249" t="s">
         <v>349</v>
       </c>
-      <c r="AL46" s="307"/>
-      <c r="AM46" s="317"/>
+      <c r="AL46" s="248"/>
+      <c r="AM46" s="255"/>
     </row>
     <row r="47" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y47" s="315"/>
-      <c r="AC47" s="316"/>
-      <c r="AH47" s="316"/>
-      <c r="AI47" s="315"/>
-      <c r="AM47" s="316"/>
+      <c r="Y47" s="253"/>
+      <c r="AC47" s="254"/>
+      <c r="AH47" s="254"/>
+      <c r="AI47" s="253"/>
+      <c r="AM47" s="254"/>
     </row>
     <row r="48" spans="3:39" ht="13.15" customHeight="1">
-      <c r="C48" s="306"/>
-      <c r="V48" s="306"/>
-      <c r="Y48" s="319"/>
-      <c r="Z48" s="320"/>
-      <c r="AA48" s="320"/>
-      <c r="AB48" s="320"/>
-      <c r="AC48" s="321"/>
-      <c r="AD48" s="320"/>
-      <c r="AE48" s="320"/>
-      <c r="AF48" s="320"/>
-      <c r="AG48" s="320"/>
-      <c r="AH48" s="321"/>
-      <c r="AI48" s="319"/>
-      <c r="AJ48" s="320"/>
-      <c r="AK48" s="320"/>
-      <c r="AL48" s="320"/>
-      <c r="AM48" s="321"/>
+      <c r="C48" s="247"/>
+      <c r="V48" s="247"/>
+      <c r="Y48" s="257"/>
+      <c r="Z48" s="258"/>
+      <c r="AA48" s="258"/>
+      <c r="AB48" s="258"/>
+      <c r="AC48" s="259"/>
+      <c r="AD48" s="258"/>
+      <c r="AE48" s="258"/>
+      <c r="AF48" s="258"/>
+      <c r="AG48" s="258"/>
+      <c r="AH48" s="259"/>
+      <c r="AI48" s="257"/>
+      <c r="AJ48" s="258"/>
+      <c r="AK48" s="258"/>
+      <c r="AL48" s="258"/>
+      <c r="AM48" s="259"/>
     </row>
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y50" s="306" t="s">
+      <c r="Y50" s="247" t="s">
         <v>350</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="308" t="s">
+      <c r="Y51" s="274" t="s">
         <v>340</v>
       </c>
-      <c r="Z51" s="309"/>
-      <c r="AA51" s="309"/>
-      <c r="AB51" s="309"/>
-      <c r="AC51" s="310"/>
-      <c r="AD51" s="308" t="s">
+      <c r="Z51" s="275"/>
+      <c r="AA51" s="275"/>
+      <c r="AB51" s="275"/>
+      <c r="AC51" s="276"/>
+      <c r="AD51" s="274" t="s">
         <v>341</v>
       </c>
-      <c r="AE51" s="309"/>
-      <c r="AF51" s="309"/>
-      <c r="AG51" s="309"/>
-      <c r="AH51" s="310"/>
-      <c r="AI51" s="308" t="s">
+      <c r="AE51" s="275"/>
+      <c r="AF51" s="275"/>
+      <c r="AG51" s="275"/>
+      <c r="AH51" s="276"/>
+      <c r="AI51" s="274" t="s">
         <v>342</v>
       </c>
-      <c r="AJ51" s="309"/>
-      <c r="AK51" s="309"/>
-      <c r="AL51" s="309"/>
-      <c r="AM51" s="310"/>
+      <c r="AJ51" s="275"/>
+      <c r="AK51" s="275"/>
+      <c r="AL51" s="275"/>
+      <c r="AM51" s="276"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
-      <c r="D52" s="307"/>
-      <c r="E52" s="311"/>
-      <c r="F52" s="307"/>
-      <c r="G52" s="307"/>
-      <c r="H52" s="307"/>
-      <c r="I52" s="307"/>
-      <c r="J52" s="311"/>
-      <c r="K52" s="307"/>
-      <c r="L52" s="307"/>
-      <c r="M52" s="307"/>
-      <c r="N52" s="307"/>
-      <c r="O52" s="311"/>
-      <c r="P52" s="307"/>
-      <c r="Q52" s="307"/>
-      <c r="W52" s="307"/>
-      <c r="X52" s="311"/>
-      <c r="Y52" s="312"/>
-      <c r="Z52" s="313"/>
-      <c r="AA52" s="313"/>
-      <c r="AB52" s="313"/>
-      <c r="AC52" s="314"/>
-      <c r="AD52" s="313"/>
-      <c r="AE52" s="313"/>
-      <c r="AF52" s="313"/>
-      <c r="AG52" s="313"/>
-      <c r="AH52" s="314"/>
-      <c r="AI52" s="312"/>
-      <c r="AJ52" s="313"/>
-      <c r="AK52" s="313"/>
-      <c r="AL52" s="313"/>
-      <c r="AM52" s="314"/>
+      <c r="D52" s="248"/>
+      <c r="E52" s="249"/>
+      <c r="F52" s="248"/>
+      <c r="G52" s="248"/>
+      <c r="H52" s="248"/>
+      <c r="I52" s="248"/>
+      <c r="J52" s="249"/>
+      <c r="K52" s="248"/>
+      <c r="L52" s="248"/>
+      <c r="M52" s="248"/>
+      <c r="N52" s="248"/>
+      <c r="O52" s="249"/>
+      <c r="P52" s="248"/>
+      <c r="Q52" s="248"/>
+      <c r="W52" s="248"/>
+      <c r="X52" s="249"/>
+      <c r="Y52" s="250"/>
+      <c r="Z52" s="251"/>
+      <c r="AA52" s="251"/>
+      <c r="AB52" s="251"/>
+      <c r="AC52" s="252"/>
+      <c r="AD52" s="251"/>
+      <c r="AE52" s="251"/>
+      <c r="AF52" s="251"/>
+      <c r="AG52" s="251"/>
+      <c r="AH52" s="252"/>
+      <c r="AI52" s="250"/>
+      <c r="AJ52" s="251"/>
+      <c r="AK52" s="251"/>
+      <c r="AL52" s="251"/>
+      <c r="AM52" s="252"/>
     </row>
     <row r="53" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y53" s="315"/>
-      <c r="AC53" s="316"/>
-      <c r="AH53" s="316"/>
-      <c r="AI53" s="315"/>
-      <c r="AM53" s="316"/>
+      <c r="Y53" s="253"/>
+      <c r="AC53" s="254"/>
+      <c r="AH53" s="254"/>
+      <c r="AI53" s="253"/>
+      <c r="AM53" s="254"/>
     </row>
     <row r="54" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y54" s="315"/>
-      <c r="Z54" s="307"/>
-      <c r="AA54" s="311" t="s">
+      <c r="Y54" s="253"/>
+      <c r="Z54" s="248"/>
+      <c r="AA54" s="249" t="s">
         <v>351</v>
       </c>
-      <c r="AB54" s="307"/>
-      <c r="AC54" s="317"/>
-      <c r="AD54" s="307"/>
-      <c r="AE54" s="307"/>
-      <c r="AF54" s="311" t="s">
+      <c r="AB54" s="248"/>
+      <c r="AC54" s="255"/>
+      <c r="AD54" s="248"/>
+      <c r="AE54" s="248"/>
+      <c r="AF54" s="249" t="s">
         <v>352</v>
       </c>
-      <c r="AG54" s="307"/>
-      <c r="AH54" s="317"/>
-      <c r="AI54" s="318"/>
-      <c r="AJ54" s="307"/>
-      <c r="AK54" s="311" t="s">
+      <c r="AG54" s="248"/>
+      <c r="AH54" s="255"/>
+      <c r="AI54" s="256"/>
+      <c r="AJ54" s="248"/>
+      <c r="AK54" s="249" t="s">
         <v>345</v>
       </c>
-      <c r="AL54" s="307"/>
-      <c r="AM54" s="317"/>
+      <c r="AL54" s="248"/>
+      <c r="AM54" s="255"/>
     </row>
     <row r="55" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y55" s="315"/>
-      <c r="AC55" s="316"/>
-      <c r="AH55" s="316"/>
-      <c r="AI55" s="315"/>
-      <c r="AM55" s="316"/>
+      <c r="Y55" s="253"/>
+      <c r="AC55" s="254"/>
+      <c r="AH55" s="254"/>
+      <c r="AI55" s="253"/>
+      <c r="AM55" s="254"/>
     </row>
     <row r="56" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y56" s="319"/>
-      <c r="Z56" s="320"/>
-      <c r="AA56" s="320"/>
-      <c r="AB56" s="320"/>
-      <c r="AC56" s="321"/>
-      <c r="AD56" s="320"/>
-      <c r="AE56" s="320"/>
-      <c r="AF56" s="320"/>
-      <c r="AG56" s="320"/>
-      <c r="AH56" s="321"/>
-      <c r="AI56" s="319"/>
-      <c r="AJ56" s="320"/>
-      <c r="AK56" s="320"/>
-      <c r="AL56" s="320"/>
-      <c r="AM56" s="321"/>
+      <c r="Y56" s="257"/>
+      <c r="Z56" s="258"/>
+      <c r="AA56" s="258"/>
+      <c r="AB56" s="258"/>
+      <c r="AC56" s="259"/>
+      <c r="AD56" s="258"/>
+      <c r="AE56" s="258"/>
+      <c r="AF56" s="258"/>
+      <c r="AG56" s="258"/>
+      <c r="AH56" s="259"/>
+      <c r="AI56" s="257"/>
+      <c r="AJ56" s="258"/>
+      <c r="AK56" s="258"/>
+      <c r="AL56" s="258"/>
+      <c r="AM56" s="259"/>
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
-      <c r="AK57" s="303" t="s">
+      <c r="AK57" s="244" t="s">
         <v>353</v>
       </c>
     </row>
@@ -29242,16 +29629,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B2:R14"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="B2:R15"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="4.453125" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="89.6328125" customWidth="1"/>
-    <col min="5" max="6" width="12.7265625" customWidth="1"/>
-    <col min="7" max="10" width="13.08984375" hidden="1" customWidth="1"/>
-    <col min="11" max="12" width="13.08984375" customWidth="1"/>
-    <col min="13" max="18" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="89.625" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="10" width="13.125" hidden="1" customWidth="1"/>
+    <col min="11" max="12" width="13.125" customWidth="1"/>
+    <col min="13" max="18" width="13.125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -29262,18 +29649,18 @@
       <c r="H2" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="252" t="s">
+      <c r="I2" s="285" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="252"/>
-      <c r="K2" s="252"/>
-      <c r="L2" s="252"/>
-      <c r="M2" s="252"/>
-      <c r="N2" s="252"/>
-      <c r="O2" s="252"/>
-      <c r="P2" s="252"/>
-      <c r="Q2" s="252"/>
-      <c r="R2" s="252"/>
+      <c r="J2" s="285"/>
+      <c r="K2" s="285"/>
+      <c r="L2" s="285"/>
+      <c r="M2" s="285"/>
+      <c r="N2" s="285"/>
+      <c r="O2" s="285"/>
+      <c r="P2" s="285"/>
+      <c r="Q2" s="285"/>
+      <c r="R2" s="285"/>
     </row>
     <row r="3" spans="2:18" ht="25.5" customHeight="1">
       <c r="C3" s="7"/>
@@ -29286,24 +29673,24 @@
       <c r="H3" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="I3" s="253" t="s">
+      <c r="I3" s="286" t="s">
         <v>223</v>
       </c>
-      <c r="J3" s="254"/>
-      <c r="K3" s="254"/>
-      <c r="L3" s="254"/>
-      <c r="M3" s="254"/>
-      <c r="N3" s="254"/>
-      <c r="O3" s="254"/>
-      <c r="P3" s="254"/>
-      <c r="Q3" s="254"/>
-      <c r="R3" s="254"/>
+      <c r="J3" s="287"/>
+      <c r="K3" s="287"/>
+      <c r="L3" s="287"/>
+      <c r="M3" s="287"/>
+      <c r="N3" s="287"/>
+      <c r="O3" s="287"/>
+      <c r="P3" s="287"/>
+      <c r="Q3" s="287"/>
+      <c r="R3" s="287"/>
     </row>
     <row r="4" spans="2:18" ht="25.5" customHeight="1">
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
       <c r="E4" s="24" t="str">
-        <f>DGET(B8:C15,"Ver.",H4:H5)</f>
+        <f>DGET(B8:C16,"Ver.",H4:H5)</f>
         <v>2.1.0</v>
       </c>
       <c r="F4" s="7"/>
@@ -29317,38 +29704,38 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="H5" s="12">
-        <f>MAX(B9:B15)</f>
+        <f>MAX(B9:B16)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.5" thickBot="1"/>
+    <row r="6" spans="2:18" ht="14.25" thickBot="1"/>
     <row r="7" spans="2:18">
-      <c r="C7" s="246" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="247"/>
-      <c r="E7" s="248" t="s">
+      <c r="C7" s="277" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="278"/>
+      <c r="E7" s="279" t="s">
         <v>2</v>
       </c>
-      <c r="F7" s="248"/>
-      <c r="G7" s="249" t="s">
+      <c r="F7" s="279"/>
+      <c r="G7" s="280" t="s">
         <v>5</v>
       </c>
-      <c r="H7" s="249"/>
-      <c r="I7" s="249"/>
-      <c r="J7" s="249"/>
-      <c r="K7" s="249"/>
-      <c r="L7" s="249"/>
-      <c r="M7" s="250" t="s">
+      <c r="H7" s="280"/>
+      <c r="I7" s="280"/>
+      <c r="J7" s="280"/>
+      <c r="K7" s="280"/>
+      <c r="L7" s="281"/>
+      <c r="M7" s="282" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="250"/>
-      <c r="O7" s="250"/>
-      <c r="P7" s="250"/>
-      <c r="Q7" s="250"/>
-      <c r="R7" s="251"/>
+      <c r="N7" s="283"/>
+      <c r="O7" s="283"/>
+      <c r="P7" s="283"/>
+      <c r="Q7" s="283"/>
+      <c r="R7" s="284"/>
     </row>
-    <row r="8" spans="2:18" ht="26.5" thickBot="1">
+    <row r="8" spans="2:18" ht="27.75" thickBot="1">
       <c r="B8" s="10" t="s">
         <v>94</v>
       </c>
@@ -29379,10 +29766,10 @@
       <c r="K8" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="20" t="s">
+      <c r="L8" s="266" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="21" t="s">
+      <c r="M8" s="261" t="s">
         <v>6</v>
       </c>
       <c r="N8" s="21" t="s">
@@ -29401,7 +29788,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="13.5" thickTop="1">
+    <row r="9" spans="2:18" ht="14.25" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -29433,10 +29820,10 @@
       <c r="K9" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="L9" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M9" s="14" t="s">
+      <c r="M9" s="262" t="s">
         <v>295</v>
       </c>
       <c r="N9" s="222">
@@ -29455,9 +29842,9 @@
         <v>43894</v>
       </c>
     </row>
-    <row r="10" spans="2:18" ht="143">
+    <row r="10" spans="2:18" ht="148.5">
       <c r="B10" s="10">
-        <f t="shared" ref="B10:B14" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
+        <f t="shared" ref="B10:B15" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -29487,10 +29874,10 @@
       <c r="K10" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="72" t="s">
         <v>298</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="263"/>
       <c r="N10" s="1"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -29533,10 +29920,10 @@
       <c r="K11" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="72" t="s">
         <v>134</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="263" t="s">
         <v>32</v>
       </c>
       <c r="N11" s="1" t="s">
@@ -29555,7 +29942,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="2:18" ht="39">
+    <row r="12" spans="2:18" ht="40.5">
       <c r="B12" s="10">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -29587,10 +29974,10 @@
       <c r="K12" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="L12" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="M12" s="14" t="s">
+      <c r="M12" s="262" t="s">
         <v>32</v>
       </c>
       <c r="N12" s="222" t="s">
@@ -29609,57 +29996,79 @@
         <v>45974</v>
       </c>
     </row>
-    <row r="13" spans="2:18" ht="143">
-      <c r="C13" s="241" t="s">
+    <row r="13" spans="2:18" ht="148.5">
+      <c r="C13" s="268" t="s">
         <v>335</v>
       </c>
-      <c r="D13" s="242" t="s">
+      <c r="D13" s="269" t="s">
         <v>338</v>
       </c>
-      <c r="E13" s="243" t="s">
+      <c r="E13" s="270" t="s">
         <v>32</v>
       </c>
-      <c r="F13" s="243" t="s">
+      <c r="F13" s="270" t="s">
         <v>32</v>
       </c>
-      <c r="G13" s="238"/>
-      <c r="H13" s="238"/>
-      <c r="I13" s="238"/>
-      <c r="J13" s="238"/>
-      <c r="K13" s="244" t="s">
+      <c r="G13" s="271"/>
+      <c r="H13" s="271"/>
+      <c r="I13" s="271"/>
+      <c r="J13" s="271"/>
+      <c r="K13" s="272" t="s">
         <v>334</v>
       </c>
-      <c r="L13" s="245">
+      <c r="L13" s="273">
         <v>46009</v>
       </c>
-      <c r="M13" s="238"/>
+      <c r="M13" s="264"/>
       <c r="N13" s="239"/>
       <c r="O13" s="238"/>
       <c r="P13" s="239"/>
       <c r="Q13" s="238"/>
       <c r="R13" s="240"/>
     </row>
-    <row r="14" spans="2:18" ht="13.5" thickBot="1">
-      <c r="B14" s="10">
+    <row r="14" spans="2:18" ht="40.5">
+      <c r="C14" s="241" t="s">
+        <v>355</v>
+      </c>
+      <c r="D14" s="260" t="s">
+        <v>354</v>
+      </c>
+      <c r="E14" s="242"/>
+      <c r="F14" s="242"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
+      <c r="K14" s="267"/>
+      <c r="L14" s="243"/>
+      <c r="M14" s="264"/>
+      <c r="N14" s="239"/>
+      <c r="O14" s="238"/>
+      <c r="P14" s="239"/>
+      <c r="Q14" s="238"/>
+      <c r="R14" s="240"/>
+    </row>
+    <row r="15" spans="2:18" ht="14.25" thickBot="1">
+      <c r="B15" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="C14" s="4"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5"/>
-      <c r="J14" s="5"/>
-      <c r="K14" s="5"/>
-      <c r="L14" s="5"/>
-      <c r="M14" s="5"/>
-      <c r="N14" s="5"/>
-      <c r="O14" s="5"/>
-      <c r="P14" s="5"/>
-      <c r="Q14" s="5"/>
-      <c r="R14" s="6"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
+      <c r="K15" s="5"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="265"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="5"/>
+      <c r="R15" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -29683,11 +30092,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.6328125" customWidth="1"/>
-    <col min="3" max="3" width="3.453125" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -29701,13 +30110,13 @@
         <v>146</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.5" thickBot="1">
+    <row r="6" spans="2:5" ht="14.25" thickBot="1">
       <c r="B6" s="150" t="s">
         <v>137</v>
       </c>
       <c r="C6" s="150"/>
     </row>
-    <row r="7" spans="2:5" ht="13.5" thickBot="1">
+    <row r="7" spans="2:5" ht="14.25" thickBot="1">
       <c r="C7" s="76" t="s">
         <v>139</v>
       </c>
@@ -29727,7 +30136,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26">
+    <row r="9" spans="2:5" ht="27">
       <c r="C9" s="160">
         <v>1</v>
       </c>
@@ -29738,7 +30147,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.5" thickBot="1">
+    <row r="10" spans="2:5" ht="14.25" thickBot="1">
       <c r="C10" s="158"/>
       <c r="D10" s="87"/>
       <c r="E10" s="6"/>
@@ -29746,14 +30155,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="156"/>
     </row>
-    <row r="12" spans="2:5" ht="13.5" thickBot="1">
+    <row r="12" spans="2:5" ht="14.25" thickBot="1">
       <c r="B12" s="151" t="s">
         <v>138</v>
       </c>
       <c r="C12" s="83"/>
       <c r="D12" s="83"/>
     </row>
-    <row r="13" spans="2:5" ht="13.5" thickBot="1">
+    <row r="13" spans="2:5" ht="14.25" thickBot="1">
       <c r="B13" s="152"/>
       <c r="C13" s="157" t="s">
         <v>139</v>
@@ -29765,7 +30174,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.5" thickTop="1">
+    <row r="14" spans="2:5" ht="14.25" thickTop="1">
       <c r="C14" s="154">
         <v>0</v>
       </c>
@@ -29842,17 +30251,17 @@
         <v>189</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.5" thickBot="1">
+    <row r="21" spans="2:5" ht="14.25" thickBot="1">
       <c r="C21" s="158"/>
       <c r="D21" s="87"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.5" thickBot="1">
+    <row r="24" spans="2:5" ht="14.25" thickBot="1">
       <c r="B24" s="150" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.5" thickBot="1">
+    <row r="25" spans="2:5" ht="14.25" thickBot="1">
       <c r="C25" s="157" t="s">
         <v>139</v>
       </c>
@@ -29939,26 +30348,26 @@
       <c r="D33" s="86"/>
       <c r="E33" s="72"/>
     </row>
-    <row r="34" spans="2:5" ht="13.5" thickBot="1">
+    <row r="34" spans="2:5" ht="14.25" thickBot="1">
       <c r="C34" s="158"/>
       <c r="D34" s="87"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.5" thickBot="1">
+    <row r="37" spans="2:5" ht="14.25" thickBot="1">
       <c r="B37" s="150" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="255"/>
-      <c r="D38" s="256"/>
+      <c r="C38" s="288"/>
+      <c r="D38" s="289"/>
       <c r="E38" s="111" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.5" thickBot="1">
-      <c r="C39" s="257"/>
-      <c r="D39" s="258"/>
+    <row r="39" spans="2:5" ht="14.25" thickBot="1">
+      <c r="C39" s="290"/>
+      <c r="D39" s="291"/>
       <c r="E39" s="6" t="s">
         <v>126</v>
       </c>
@@ -29984,133 +30393,133 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.7265625" customWidth="1"/>
-    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="284" t="s">
+      <c r="B2" s="292" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="285"/>
-      <c r="D2" s="272" t="s">
+      <c r="C2" s="293"/>
+      <c r="D2" s="298" t="s">
         <v>336</v>
       </c>
-      <c r="E2" s="273"/>
-      <c r="F2" s="273"/>
-      <c r="G2" s="273"/>
-      <c r="H2" s="274"/>
+      <c r="E2" s="299"/>
+      <c r="F2" s="299"/>
+      <c r="G2" s="299"/>
+      <c r="H2" s="300"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="259" t="s">
+      <c r="B3" s="294" t="s">
         <v>122</v>
       </c>
-      <c r="C3" s="260"/>
-      <c r="D3" s="275" t="s">
+      <c r="C3" s="295"/>
+      <c r="D3" s="301" t="s">
         <v>337</v>
       </c>
-      <c r="E3" s="276"/>
-      <c r="F3" s="276"/>
-      <c r="G3" s="276"/>
-      <c r="H3" s="277"/>
+      <c r="E3" s="302"/>
+      <c r="F3" s="302"/>
+      <c r="G3" s="302"/>
+      <c r="H3" s="303"/>
     </row>
-    <row r="4" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B4" s="270" t="s">
+    <row r="4" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B4" s="296" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="271"/>
-      <c r="D4" s="278" t="str">
+      <c r="C4" s="297"/>
+      <c r="D4" s="304" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_H_DRIPOW-CSTD-1-00-B-C0.c</v>
       </c>
-      <c r="E4" s="279"/>
-      <c r="F4" s="279"/>
-      <c r="G4" s="279"/>
-      <c r="H4" s="280"/>
+      <c r="E4" s="305"/>
+      <c r="F4" s="305"/>
+      <c r="G4" s="305"/>
+      <c r="H4" s="306"/>
     </row>
-    <row r="5" spans="2:14" ht="13.5" thickBot="1">
+    <row r="5" spans="2:14" ht="14.25" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="284" t="s">
+      <c r="B6" s="292" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="285"/>
-      <c r="D6" s="281" t="str">
+      <c r="C6" s="293"/>
+      <c r="D6" s="307" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>H_DRIPOW</v>
       </c>
-      <c r="E6" s="282"/>
-      <c r="F6" s="282"/>
-      <c r="G6" s="282"/>
-      <c r="H6" s="283"/>
+      <c r="E6" s="308"/>
+      <c r="F6" s="308"/>
+      <c r="G6" s="308"/>
+      <c r="H6" s="309"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="259" t="s">
+      <c r="B7" s="294" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="260"/>
-      <c r="D7" s="261">
+      <c r="C7" s="295"/>
+      <c r="D7" s="310">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="262"/>
-      <c r="F7" s="262"/>
-      <c r="G7" s="262"/>
-      <c r="H7" s="263"/>
+      <c r="E7" s="311"/>
+      <c r="F7" s="311"/>
+      <c r="G7" s="311"/>
+      <c r="H7" s="312"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="259" t="s">
+      <c r="B8" s="294" t="s">
         <v>98</v>
       </c>
-      <c r="C8" s="260"/>
-      <c r="D8" s="261" t="str">
+      <c r="C8" s="295"/>
+      <c r="D8" s="310" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_H_DRIPOW_MTRX</v>
       </c>
-      <c r="E8" s="262"/>
-      <c r="F8" s="262"/>
-      <c r="G8" s="262"/>
-      <c r="H8" s="263"/>
+      <c r="E8" s="311"/>
+      <c r="F8" s="311"/>
+      <c r="G8" s="311"/>
+      <c r="H8" s="312"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="259" t="s">
+      <c r="B9" s="294" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="260"/>
-      <c r="D9" s="264" t="s">
+      <c r="C9" s="295"/>
+      <c r="D9" s="313" t="s">
         <v>231</v>
       </c>
-      <c r="E9" s="265"/>
-      <c r="F9" s="265"/>
-      <c r="G9" s="265"/>
-      <c r="H9" s="266"/>
+      <c r="E9" s="314"/>
+      <c r="F9" s="314"/>
+      <c r="G9" s="314"/>
+      <c r="H9" s="315"/>
     </row>
-    <row r="10" spans="2:14" ht="13.5" thickBot="1">
-      <c r="B10" s="270" t="s">
+    <row r="10" spans="2:14" ht="14.25" thickBot="1">
+      <c r="B10" s="296" t="s">
         <v>45</v>
       </c>
-      <c r="C10" s="271"/>
-      <c r="D10" s="267">
+      <c r="C10" s="297"/>
+      <c r="D10" s="316">
         <v>80</v>
       </c>
-      <c r="E10" s="268"/>
-      <c r="F10" s="268"/>
-      <c r="G10" s="268"/>
-      <c r="H10" s="269"/>
+      <c r="E10" s="317"/>
+      <c r="F10" s="317"/>
+      <c r="G10" s="317"/>
+      <c r="H10" s="318"/>
     </row>
-    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.5" thickBot="1">
+    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="12" spans="2:14" ht="14.25" thickBot="1">
       <c r="B12" s="141" t="s">
         <v>35</v>
       </c>
@@ -30145,7 +30554,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.5" thickTop="1">
+    <row r="13" spans="2:14" ht="14.25" thickTop="1">
       <c r="B13" s="105">
         <v>1</v>
       </c>
@@ -30998,7 +31407,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.5" thickBot="1">
+    <row r="37" spans="2:14" ht="14.25" thickBot="1">
       <c r="B37" s="96">
         <v>25</v>
       </c>
@@ -31039,22 +31448,22 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
@@ -31094,21 +31503,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.453125" customWidth="1"/>
-    <col min="6" max="6" width="52.7265625" customWidth="1"/>
-    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.90625" customWidth="1"/>
-    <col min="16" max="16" width="9.90625" customWidth="1"/>
-    <col min="17" max="17" width="44.6328125" customWidth="1"/>
-    <col min="18" max="18" width="73.6328125" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.5" thickBot="1">
+    <row r="2" spans="2:18" ht="14.25" thickBot="1">
       <c r="B2" t="s">
         <v>212</v>
       </c>
@@ -31116,7 +31525,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.5" thickBot="1">
+    <row r="3" spans="2:18" ht="14.25" thickBot="1">
       <c r="B3" s="141" t="s">
         <v>35</v>
       </c>
@@ -31154,7 +31563,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B4" s="172">
         <v>0</v>
       </c>
@@ -31182,7 +31591,7 @@
       </c>
       <c r="R4" s="140"/>
     </row>
-    <row r="5" spans="2:18" ht="13.5" thickTop="1">
+    <row r="5" spans="2:18" ht="14.25" thickTop="1">
       <c r="B5" s="175">
         <v>1</v>
       </c>
@@ -31710,7 +32119,7 @@
       <c r="Q28" s="145"/>
       <c r="R28" s="116"/>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="176">
         <v>25</v>
       </c>
@@ -31732,7 +32141,7 @@
       <c r="Q29" s="143"/>
       <c r="R29" s="118"/>
     </row>
-    <row r="32" spans="2:18" ht="13.5" thickBot="1">
+    <row r="32" spans="2:18" ht="14.25" thickBot="1">
       <c r="B32" t="s">
         <v>213</v>
       </c>
@@ -31740,7 +32149,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.5" thickBot="1">
+    <row r="33" spans="2:18" ht="14.25" thickBot="1">
       <c r="B33" s="141" t="s">
         <v>35</v>
       </c>
@@ -31772,7 +32181,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
       <c r="B34" s="172">
         <v>0</v>
       </c>
@@ -31798,7 +32207,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.5" thickTop="1">
+    <row r="35" spans="2:18" ht="14.25" thickTop="1">
       <c r="B35" s="175">
         <v>1</v>
       </c>
@@ -32326,7 +32735,7 @@
       <c r="Q58" s="145"/>
       <c r="R58" s="177"/>
     </row>
-    <row r="59" spans="2:18" ht="13.5" thickBot="1">
+    <row r="59" spans="2:18" ht="14.25" thickBot="1">
       <c r="B59" s="176">
         <v>25</v>
       </c>
@@ -32374,29 +32783,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="28.36328125" customWidth="1"/>
-    <col min="3" max="3" width="15.90625" customWidth="1"/>
-    <col min="5" max="5" width="12.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.7265625" customWidth="1"/>
-    <col min="7" max="7" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.36328125" customWidth="1"/>
-    <col min="10" max="10" width="34.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.36328125" customWidth="1"/>
-    <col min="12" max="12" width="16.08984375" customWidth="1"/>
-    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="34.125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.5" thickBot="1">
+    <row r="1" spans="2:21" ht="14.25" thickBot="1">
       <c r="C1" s="89" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.5" thickBot="1">
+    <row r="2" spans="2:21" ht="14.25" thickBot="1">
       <c r="B2" s="97" t="s">
         <v>59</v>
       </c>
@@ -32440,7 +32849,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="26"/>
       <c r="C3" s="48" t="s">
         <v>111</v>
@@ -32461,7 +32870,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.5" thickTop="1">
+    <row r="4" spans="2:21" ht="14.25" thickTop="1">
       <c r="B4" s="26" t="s">
         <v>254</v>
       </c>
@@ -32839,7 +33248,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.5" thickBot="1">
+    <row r="13" spans="2:21" ht="14.25" thickBot="1">
       <c r="B13" s="26"/>
       <c r="C13" s="25"/>
       <c r="D13" s="115"/>
@@ -35090,7 +35499,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.5" thickBot="1">
+    <row r="103" spans="2:15" ht="14.25" thickBot="1">
       <c r="B103" s="50"/>
       <c r="C103" s="51"/>
       <c r="D103" s="117"/>
@@ -35159,18 +35568,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.08984375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.08984375" customWidth="1"/>
-    <col min="48" max="48" width="23.6328125" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -35186,7 +35595,7 @@
       <c r="B2" s="125" t="s">
         <v>130</v>
       </c>
-      <c r="C2" s="286" t="s">
+      <c r="C2" s="319" t="s">
         <v>85</v>
       </c>
       <c r="D2" s="55">
@@ -35285,7 +35694,7 @@
       <c r="AI2" s="55">
         <v>0</v>
       </c>
-      <c r="AJ2" s="288" t="s">
+      <c r="AJ2" s="321" t="s">
         <v>164</v>
       </c>
     </row>
@@ -35293,7 +35702,7 @@
       <c r="B3" s="132" t="s">
         <v>234</v>
       </c>
-      <c r="C3" s="287"/>
+      <c r="C3" s="320"/>
       <c r="D3" s="127" t="s">
         <v>62</v>
       </c>
@@ -35381,21 +35790,21 @@
       <c r="AF3" s="188" t="s">
         <v>253</v>
       </c>
-      <c r="AG3" s="294" t="s">
+      <c r="AG3" s="327" t="s">
         <v>274</v>
       </c>
-      <c r="AH3" s="295"/>
-      <c r="AI3" s="296"/>
-      <c r="AJ3" s="289"/>
+      <c r="AH3" s="328"/>
+      <c r="AI3" s="329"/>
+      <c r="AJ3" s="322"/>
       <c r="AR3" s="90" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A4" s="290" t="s">
+    <row r="4" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A4" s="323" t="s">
         <v>64</v>
       </c>
-      <c r="B4" s="291"/>
+      <c r="B4" s="324"/>
       <c r="C4" s="137"/>
       <c r="D4" s="137"/>
       <c r="E4" s="137"/>
@@ -35439,9 +35848,9 @@
       <c r="AV4" s="79"/>
       <c r="AW4" s="80"/>
     </row>
-    <row r="5" spans="1:49" ht="13.5" thickBot="1">
-      <c r="A5" s="292"/>
-      <c r="B5" s="293"/>
+    <row r="5" spans="1:49" ht="14.25" thickBot="1">
+      <c r="A5" s="325"/>
+      <c r="B5" s="326"/>
       <c r="C5" s="138"/>
       <c r="D5" s="138"/>
       <c r="E5" s="138"/>
@@ -36956,7 +37365,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.5" thickBot="1">
+    <row r="17" spans="2:49" ht="14.25" thickBot="1">
       <c r="B17" s="134"/>
       <c r="C17" s="44">
         <f t="shared" si="2"/>
@@ -43368,7 +43777,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.5" thickBot="1">
+    <row r="70" spans="1:46" ht="14.25" thickBot="1">
       <c r="A70" s="53" t="s">
         <v>65</v>
       </c>
@@ -64006,36 +64415,36 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AW266"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="43.36328125" customWidth="1"/>
-    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="2" max="2" width="43.375" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
     <col min="11" max="11" width="22" customWidth="1"/>
     <col min="12" max="12" width="17" customWidth="1"/>
-    <col min="13" max="13" width="37.08984375" customWidth="1"/>
-    <col min="14" max="14" width="20.90625" customWidth="1"/>
-    <col min="15" max="18" width="10.90625" customWidth="1"/>
+    <col min="13" max="13" width="37.125" customWidth="1"/>
+    <col min="14" max="14" width="20.875" customWidth="1"/>
+    <col min="15" max="18" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:48" ht="14.5" thickBot="1">
+    <row r="2" spans="2:48" ht="15" thickBot="1">
       <c r="B2" s="27" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="3" spans="2:48" ht="14.5" thickBot="1">
+    <row r="3" spans="2:48" ht="15" thickBot="1">
       <c r="B3" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="C3" s="300" t="s">
+      <c r="C3" s="333" t="s">
         <v>229</v>
       </c>
-      <c r="D3" s="301"/>
-      <c r="E3" s="301"/>
-      <c r="F3" s="301"/>
-      <c r="G3" s="301"/>
-      <c r="H3" s="301"/>
-      <c r="I3" s="301"/>
-      <c r="J3" s="302"/>
+      <c r="D3" s="334"/>
+      <c r="E3" s="334"/>
+      <c r="F3" s="334"/>
+      <c r="G3" s="334"/>
+      <c r="H3" s="334"/>
+      <c r="I3" s="334"/>
+      <c r="J3" s="335"/>
       <c r="K3" s="226"/>
       <c r="L3" s="168"/>
       <c r="M3" s="168"/>
@@ -64103,16 +64512,16 @@
       <c r="B5" s="68" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="297" t="s">
+      <c r="C5" s="330" t="s">
         <v>190</v>
       </c>
-      <c r="D5" s="298"/>
-      <c r="E5" s="298"/>
-      <c r="F5" s="298"/>
-      <c r="G5" s="298"/>
-      <c r="H5" s="298"/>
-      <c r="I5" s="298"/>
-      <c r="J5" s="298"/>
+      <c r="D5" s="331"/>
+      <c r="E5" s="331"/>
+      <c r="F5" s="331"/>
+      <c r="G5" s="331"/>
+      <c r="H5" s="331"/>
+      <c r="I5" s="331"/>
+      <c r="J5" s="331"/>
       <c r="K5" s="230" t="s">
         <v>318</v>
       </c>
@@ -64136,7 +64545,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:48" ht="26">
+    <row r="6" spans="2:48" ht="27">
       <c r="B6" s="68" t="s">
         <v>34</v>
       </c>
@@ -64187,16 +64596,16 @@
       <c r="B7" s="69" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="299" t="s">
+      <c r="C7" s="332" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="298"/>
-      <c r="E7" s="298"/>
-      <c r="F7" s="298"/>
-      <c r="G7" s="298"/>
-      <c r="H7" s="298"/>
-      <c r="I7" s="298"/>
-      <c r="J7" s="298"/>
+      <c r="D7" s="331"/>
+      <c r="E7" s="331"/>
+      <c r="F7" s="331"/>
+      <c r="G7" s="331"/>
+      <c r="H7" s="331"/>
+      <c r="I7" s="331"/>
+      <c r="J7" s="331"/>
       <c r="K7" s="230" t="s">
         <v>134</v>
       </c>
@@ -64214,7 +64623,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="8" spans="2:48" ht="131">
+    <row r="8" spans="2:48" ht="136.5">
       <c r="B8" s="68" t="s">
         <v>29</v>
       </c>
@@ -64771,7 +65180,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="19" spans="2:18" ht="13.5" thickBot="1">
+    <row r="19" spans="2:18" ht="14.25" thickBot="1">
       <c r="B19" s="189" t="s">
         <v>293</v>
       </c>
@@ -65281,7 +65690,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="29" spans="2:18" ht="13.5" thickBot="1">
+    <row r="29" spans="2:18" ht="14.25" thickBot="1">
       <c r="B29" s="189" t="s">
         <v>293</v>
       </c>
@@ -65460,14 +65869,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
-    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.26953125" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.5" thickBot="1">
+    <row r="2" spans="2:4" ht="14.25" thickBot="1">
       <c r="B2" s="82" t="s">
         <v>88</v>
       </c>
@@ -65477,7 +65886,7 @@
       </c>
       <c r="D2" s="83"/>
     </row>
-    <row r="3" spans="2:4" ht="13.5" thickBot="1">
+    <row r="3" spans="2:4" ht="14.25" thickBot="1">
       <c r="B3" s="76" t="s">
         <v>86</v>
       </c>
@@ -65488,7 +65897,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.5" thickTop="1">
+    <row r="4" spans="2:4" ht="14.25" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -65499,7 +65908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39">
+    <row r="5" spans="2:4" ht="40.5">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -65510,7 +65919,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26">
+    <row r="6" spans="2:4" ht="27">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -65521,7 +65930,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52">
+    <row r="7" spans="2:4" ht="54">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -65532,7 +65941,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="78">
+    <row r="8" spans="2:4" ht="81">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -65554,7 +65963,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26">
+    <row r="10" spans="2:4" ht="27">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -65565,7 +65974,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26">
+    <row r="11" spans="2:4" ht="27">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -65576,7 +65985,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26">
+    <row r="12" spans="2:4" ht="27">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -65587,7 +65996,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26">
+    <row r="13" spans="2:4" ht="27">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -65598,7 +66007,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26">
+    <row r="14" spans="2:4" ht="27">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -65609,7 +66018,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="130">
+    <row r="15" spans="2:4" ht="135">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -65631,7 +66040,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26">
+    <row r="17" spans="2:4" ht="27">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -65642,7 +66051,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="91">
+    <row r="18" spans="2:4" ht="67.5">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -65653,7 +66062,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39">
+    <row r="19" spans="2:4" ht="40.5">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -65711,7 +66120,7 @@
       <c r="C26" s="86"/>
       <c r="D26" s="72"/>
     </row>
-    <row r="27" spans="2:4" ht="13.5" thickBot="1">
+    <row r="27" spans="2:4" ht="14.25" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="87"/>
       <c r="D27" s="6"/>
